--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Redaa29a541ae456a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R6d8195982b124e40"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -343,7 +343,7 @@
         <x:v>任务ID</x:v>
       </x:c>
       <x:c r="B2" s="9" t="str">
-        <x:v>playwright_account_freeze_release_audit</x:v>
+        <x:v>playwright_account_freeze_release_review</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
@@ -471,12 +471,12 @@
         <x:v>完成条件</x:v>
       </x:c>
       <x:c r="B18" s="9" t="str">
-        <x:v>npm run audit返回0，六个目标路径可读，四份报告按业务主键闭合</x:v>
+        <x:v>运行入口生成题面所列配置、用例和报告，四份报告按业务主键关联</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="47" customHeight="1">
       <x:c r="A19" s="9" t="str">
-        <x:v>可验证点</x:v>
+        <x:v>业务核对点</x:v>
       </x:c>
       <x:c r="B19" s="9" t="str">
         <x:v>浏览器项目、时区、页面卡片顺序、裁决徽标、按钮状态、TOTP窗口、焦点次序、冻结请求合同与跨报告追溯</x:v>

--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R6d8195982b124e40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R04e731bca28948ea"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -367,7 +367,7 @@
         <x:v>输入来源</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>自造并脱敏的账号安全发布演练，包括静态控制台、风险登录事件、值班角色、冻结策略和待处理队列</x:v>
+        <x:v>本次账号安全控制台发布批次，包括字段已脱敏的风险登录事件、值班角色、冻结策略和待处理队列</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="47" customHeight="1">
@@ -410,12 +410,12 @@
         <x:v>queue_item_id唯一，review_queue.csv中的event_id必须在风险事件中唯一命中，并保留对应account_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="62" customHeight="1">
+    <x:row r="11" ht="47" customHeight="1">
       <x:c r="A11" s="9" t="str">
         <x:v>裁决优先级</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>按already_locked、staff_escalation、service_account_escalation、freeze_high_risk、manual_review、monitor顺序裁决</x:v>
+        <x:v>按freeze_policy.json中的decision_order逐项判断，首个命中的条件决定页面处置和reason_code</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="47" customHeight="1">
@@ -426,12 +426,12 @@
         <x:v>账号裁决为freeze、队列角色等于active_role、角色允许冻结该账号类型且冻结量不超过daily_freeze_limit</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="47" customHeight="1">
+    <x:row r="13" ht="62" customHeight="1">
       <x:c r="A13" s="9" t="str">
         <x:v>验证码窗口</x:v>
       </x:c>
       <x:c r="B13" s="9" t="str">
-        <x:v>按fixed_now_utc、secret_base32、HMAC-SHA1、30秒步长、6位和偏移集合计算TOTP</x:v>
+        <x:v>按freeze_policy.json中的fixed_now_utc、secret_base32、algorithm、digits、step_seconds和accepted_step_offsets计算TOTP</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="47" customHeight="1">
@@ -466,27 +466,35 @@
         <x:v>app、fixtures、queues和starter保持不变，正式运行只访问本机回环地址</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="32" customHeight="1">
+    <x:row r="18" ht="47" customHeight="1">
       <x:c r="A18" s="9" t="str">
+        <x:v>实现边界</x:v>
+      </x:c>
+      <x:c r="B18" s="9" t="str">
+        <x:v>输入页面、事件、角色、策略和队列保持只读，不连接账号系统或风控服务，配置、测试源码和四份报告只写入output目录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="32" customHeight="1">
+      <x:c r="A19" s="9" t="str">
         <x:v>完成条件</x:v>
       </x:c>
-      <x:c r="B18" s="9" t="str">
+      <x:c r="B19" s="9" t="str">
         <x:v>运行入口生成题面所列配置、用例和报告，四份报告按业务主键关联</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="47" customHeight="1">
-      <x:c r="A19" s="9" t="str">
-        <x:v>业务核对点</x:v>
-      </x:c>
-      <x:c r="B19" s="9" t="str">
-        <x:v>浏览器项目、时区、页面卡片顺序、裁决徽标、按钮状态、TOTP窗口、焦点次序、冻结请求合同与跨报告追溯</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="47" customHeight="1">
       <x:c r="A20" s="9" t="str">
+        <x:v>可验证点</x:v>
+      </x:c>
+      <x:c r="B20" s="9" t="str">
+        <x:v>浏览器项目、时区、页面卡片顺序、裁决徽标、按钮状态、TOTP窗口、焦点次序、冻结请求合同和跨报告追溯均有对应交付记录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="47" customHeight="1">
+      <x:c r="A21" s="9" t="str">
         <x:v>不适合作为评分点的内容</x:v>
       </x:c>
-      <x:c r="B20" s="9" t="str">
+      <x:c r="B21" s="9" t="str">
         <x:v>辅助函数拆分、变量名、注释、内部对象、等价定位器、CSV必要引号以及LF或CRLF行尾</x:v>
       </x:c>
     </x:row>
